--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审批意见" sheetId="3" r:id="rId1"/>
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +52,7 @@
     <t>日期：</t>
   </si>
   <si>
-    <t>{expDate}</t>
+    <t>{expDateStr}</t>
   </si>
   <si>
     <t>流水号：</t>
@@ -106,7 +106,7 @@
     <t>{item.expItem}</t>
   </si>
   <si>
-    <t>{item.desc}</t>
+    <t>{item.descMemo}</t>
   </si>
   <si>
     <t>{item.applyAmount}</t>
@@ -197,7 +197,7 @@
     <t>{cost.expItem}</t>
   </si>
   <si>
-    <t>{cost.desc}</t>
+    <t>{cost.descMemo}</t>
   </si>
   <si>
     <t>{cost.applyAmount}</t>
@@ -1024,7 +1024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1050,6 +1050,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1831,45 +1834,45 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:11">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:11">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:11">
       <c r="A4" s="5" t="s">
@@ -1895,214 +1898,214 @@
       <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="36"/>
+      <c r="K4" s="37"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:11">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="20" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="20" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="22"/>
-      <c r="J5" s="20" t="s">
+      <c r="I5" s="23"/>
+      <c r="J5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="22"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:11">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="26" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="26" t="s">
+      <c r="G6" s="28"/>
+      <c r="H6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="27"/>
-      <c r="J6" s="26" t="s">
+      <c r="I6" s="28"/>
+      <c r="J6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="28"/>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:11">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="9" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="28" t="s">
+      <c r="I7" s="10"/>
+      <c r="J7" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="37"/>
+      <c r="K7" s="38"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:11">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="13" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="38" t="s">
+      <c r="I8" s="14"/>
+      <c r="J8" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="39"/>
+      <c r="K8" s="40"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="13" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="9" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="10"/>
+      <c r="J9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="13" t="s">
+      <c r="B10" s="10"/>
+      <c r="C10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="13" t="s">
+      <c r="G10" s="10"/>
+      <c r="H10" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13" t="s">
+      <c r="I10" s="14"/>
+      <c r="J10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" ht="150" customHeight="1" spans="1:11">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:11">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:11">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35" t="s">
+      <c r="D13" s="36"/>
+      <c r="E13" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="9" t="s">
+      <c r="F13" s="36"/>
+      <c r="G13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:11">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35" t="s">
+      <c r="D14" s="36"/>
+      <c r="E14" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35" t="s">
+      <c r="F14" s="36"/>
+      <c r="G14" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2148,7 +2151,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="36" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2209,125 +2212,125 @@
       <c r="G2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="16"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9" t="s">
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" ht="409.5" customHeight="1" spans="1:11">
-      <c r="A4" s="10" t="s">
+    <row r="4" ht="175" customHeight="1" spans="1:11">
+      <c r="A4" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
+      <c r="H4" s="13"/>
+      <c r="I4" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13" t="s">
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
-    <row r="7" ht="62.1" customHeight="1" spans="1:11">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+    <row r="7" ht="24" customHeight="1" spans="1:11">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2347,7 +2350,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="33" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -11,8 +11,8 @@
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15,报销单与审批意见!$X$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t xml:space="preserve"> {company}费用报销单</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>{costTaxAmountTotal}</t>
+  </si>
+  <si>
+    <t>公司名称</t>
+  </si>
+  <si>
+    <t>{company}</t>
   </si>
 </sst>
 </file>
@@ -237,7 +243,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,13 +268,6 @@
     </font>
     <font>
       <sz val="25"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -894,137 +893,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1070,16 +1069,10 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1130,13 +1123,13 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1834,45 +1827,45 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="1:11">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:11">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:11">
       <c r="A4" s="5" t="s">
@@ -1898,56 +1891,56 @@
       <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="37"/>
+      <c r="K4" s="35"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:11">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="20"/>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="21" t="s">
+      <c r="D5" s="20"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="21" t="s">
+      <c r="G5" s="21"/>
+      <c r="H5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="21" t="s">
+      <c r="I5" s="21"/>
+      <c r="J5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="23"/>
+      <c r="K5" s="21"/>
     </row>
     <row r="6" ht="60" customHeight="1" spans="1:11">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="24" t="s">
+      <c r="B6" s="23"/>
+      <c r="C6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="27" t="s">
+      <c r="D6" s="24"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="27" t="s">
+      <c r="G6" s="26"/>
+      <c r="H6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="27" t="s">
+      <c r="I6" s="26"/>
+      <c r="J6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="28"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" ht="60" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
@@ -1960,36 +1953,36 @@
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
-      <c r="G7" s="29"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="10" t="s">
         <v>21</v>
       </c>
       <c r="I7" s="10"/>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="38"/>
+      <c r="K7" s="36"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:11">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="30" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="14" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="14"/>
-      <c r="J8" s="39" t="s">
+      <c r="J8" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="40"/>
+      <c r="K8" s="38"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
       <c r="A9" s="10" t="s">
@@ -2038,46 +2031,46 @@
       <c r="K10" s="14"/>
     </row>
     <row r="11" ht="150" customHeight="1" spans="1:11">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
     </row>
     <row r="12" ht="90" customHeight="1" spans="1:11">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
     </row>
     <row r="13" ht="60" customHeight="1" spans="1:11">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36" t="s">
+      <c r="B13" s="34"/>
+      <c r="C13" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36" t="s">
+      <c r="D13" s="34"/>
+      <c r="E13" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="36"/>
+      <c r="F13" s="34"/>
       <c r="G13" s="10" t="s">
         <v>41</v>
       </c>
@@ -2087,25 +2080,25 @@
       <c r="K13" s="10"/>
     </row>
     <row r="14" ht="60" customHeight="1" spans="1:11">
-      <c r="A14" s="36" t="s">
+      <c r="A14" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36" t="s">
+      <c r="B14" s="34"/>
+      <c r="C14" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36" t="s">
+      <c r="D14" s="34"/>
+      <c r="E14" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36" t="s">
+      <c r="F14" s="34"/>
+      <c r="G14" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2218,10 +2211,10 @@
       <c r="I2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="17"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="10" t="s">
@@ -2319,21 +2312,25 @@
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="1:11">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+    <row r="7" ht="85" customHeight="1" spans="1:11">
+      <c r="A7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="J2:K2"/>
@@ -2347,6 +2344,8 @@
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="报销单与审批意见" sheetId="3" r:id="rId1"/>
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15,报销单与审批意见!$X$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$11,报销单与审批意见!$X$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
   <si>
     <t xml:space="preserve"> {company}费用报销单</t>
   </si>
@@ -143,33 +143,6 @@
   </si>
   <si>
     <t>{verifyPayAmount}</t>
-  </si>
-  <si>
-    <t>审批意见</t>
-  </si>
-  <si>
-    <t>节点名称</t>
-  </si>
-  <si>
-    <t>操作人</t>
-  </si>
-  <si>
-    <t>操作类型</t>
-  </si>
-  <si>
-    <t>意见</t>
-  </si>
-  <si>
-    <t>{commentList.taskName}</t>
-  </si>
-  <si>
-    <t>{commentList.userName}</t>
-  </si>
-  <si>
-    <t>{commentList.operateText}</t>
-  </si>
-  <si>
-    <t>{commentList.comment}</t>
   </si>
   <si>
     <t xml:space="preserve">成本一览表
@@ -234,16 +207,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,14 +254,6 @@
     <font>
       <b/>
       <sz val="48"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="26"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -893,137 +857,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1116,18 +1080,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1458,57 +1410,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1270</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>979170</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>186055</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>979170</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp>
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="5" name="直接连接符 4"/>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1270" y="9106535"/>
-          <a:ext cx="21111210" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-          <a:prstDash val="dash"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:prstClr val="black"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:srgbClr val="FFFFFF"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1809,7 +1710,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.125" style="2" customWidth="1"/>
@@ -1891,10 +1792,10 @@
       <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="35"/>
+      <c r="K4" s="31"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:11">
       <c r="A5" s="17" t="s">
@@ -1961,7 +1862,7 @@
       <c r="J7" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="36"/>
+      <c r="K7" s="32"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:11">
       <c r="A8" s="28" t="s">
@@ -1979,10 +1880,10 @@
         <v>25</v>
       </c>
       <c r="I8" s="14"/>
-      <c r="J8" s="37" t="s">
+      <c r="J8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="38"/>
+      <c r="K8" s="34"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
       <c r="A9" s="10" t="s">
@@ -2030,78 +1931,8 @@
       </c>
       <c r="K10" s="14"/>
     </row>
-    <row r="11" ht="150" customHeight="1" spans="1:11">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-    </row>
-    <row r="12" ht="90" customHeight="1" spans="1:11">
-      <c r="A12" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
-    </row>
-    <row r="13" ht="60" customHeight="1" spans="1:11">
-      <c r="A13" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-    </row>
-    <row r="14" ht="60" customHeight="1" spans="1:11">
-      <c r="A14" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="30">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="A5:B5"/>
@@ -2131,15 +1962,6 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:K13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:K14"/>
     <mergeCell ref="A1:K3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -2174,7 +1996,7 @@
   <sheetData>
     <row r="1" ht="132" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2218,13 +2040,13 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="10" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>20</v>
@@ -2239,39 +2061,39 @@
         <v>22</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="175" customHeight="1" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="13" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
@@ -2288,38 +2110,38 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
       <c r="A6" s="14" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
     </row>
     <row r="7" ht="85" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$11,报销单与审批意见!$X$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15,报销单与审批意见!$X$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
   <si>
     <t xml:space="preserve"> {company}费用报销单</t>
   </si>
@@ -143,6 +143,27 @@
   </si>
   <si>
     <t>{verifyPayAmount}</t>
+  </si>
+  <si>
+    <t>审批意见</t>
+  </si>
+  <si>
+    <t>节点名称</t>
+  </si>
+  <si>
+    <t>操作人</t>
+  </si>
+  <si>
+    <t>操作类型</t>
+  </si>
+  <si>
+    <t>{commentList.taskName}</t>
+  </si>
+  <si>
+    <t>{commentList.userName}</t>
+  </si>
+  <si>
+    <t>{commentList.operateText}</t>
   </si>
   <si>
     <t xml:space="preserve">成本一览表
@@ -207,15 +228,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +276,14 @@
     <font>
       <b/>
       <sz val="48"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -857,137 +887,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1080,6 +1110,33 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1410,6 +1467,57 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1270</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>979170</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>186055</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>979170</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直接连接符 4"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1270" y="9106535"/>
+          <a:ext cx="21111210" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:prstClr val="black"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1710,7 +1818,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.125" style="2" customWidth="1"/>
@@ -1792,10 +1900,10 @@
       <c r="I4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="40"/>
     </row>
     <row r="5" ht="60" customHeight="1" spans="1:11">
       <c r="A5" s="17" t="s">
@@ -1862,7 +1970,7 @@
       <c r="J7" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="32"/>
+      <c r="K7" s="41"/>
     </row>
     <row r="8" ht="99.95" customHeight="1" spans="1:11">
       <c r="A8" s="28" t="s">
@@ -1880,10 +1988,10 @@
         <v>25</v>
       </c>
       <c r="I8" s="14"/>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="34"/>
+      <c r="K8" s="43"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
       <c r="A9" s="10" t="s">
@@ -1931,8 +2039,74 @@
       </c>
       <c r="K10" s="14"/>
     </row>
+    <row r="11" ht="150" customHeight="1" spans="1:11">
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+    </row>
+    <row r="12" ht="90" customHeight="1" spans="1:11">
+      <c r="A12" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:11">
+      <c r="A13" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="38"/>
+      <c r="G13" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:11">
+      <c r="A14" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="38"/>
+      <c r="G14" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="37">
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="A5:B5"/>
@@ -1962,6 +2136,13 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:K14"/>
     <mergeCell ref="A1:K3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -1996,7 +2177,7 @@
   <sheetData>
     <row r="1" ht="132" customHeight="1" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2040,13 +2221,13 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
       <c r="A3" s="10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>20</v>
@@ -2061,39 +2242,39 @@
         <v>22</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="175" customHeight="1" spans="1:11">
       <c r="A4" s="11" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
       <c r="G4" s="13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="80.1" customHeight="1" spans="1:11">
@@ -2110,38 +2291,38 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
     </row>
     <row r="6" ht="80.1" customHeight="1" spans="1:11">
       <c r="A6" s="14" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
       <c r="H6" s="14"/>
       <c r="I6" s="14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
     </row>
     <row r="7" ht="85" customHeight="1" spans="1:11">
       <c r="A7" s="10" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15,报销单与审批意见!$X$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$55</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -61,13 +61,13 @@
     <t>{sn}</t>
   </si>
   <si>
-    <t>借支余额</t>
-  </si>
-  <si>
-    <t>本次冲借支</t>
-  </si>
-  <si>
-    <t>借支单编码</t>
+    <t>冲账类型</t>
+  </si>
+  <si>
+    <t>本次冲账金额</t>
+  </si>
+  <si>
+    <t>冲账单据编码</t>
   </si>
   <si>
     <t>项目合同编号</t>
@@ -76,7 +76,7 @@
     <t>研发编号</t>
   </si>
   <si>
-    <t>{cashBalance}</t>
+    <t>{offsetType}</t>
   </si>
   <si>
     <t>{offsetAmount}</t>
@@ -127,13 +127,13 @@
     <t>核定付款金额</t>
   </si>
   <si>
-    <t>核定冲借支的金额</t>
+    <t>核定冲账金额</t>
   </si>
   <si>
     <t>{verifyOffsetAmount}</t>
   </si>
   <si>
-    <t>核定借支单编码</t>
+    <t>核定编码</t>
   </si>
   <si>
     <t>{verifyCashSn}</t>

--- a/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
+++ b/snowy-plugin/snowy-plugin-biz/snowy-plugin-biz-func/src/main/resources/Fee_Template.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="报销单与审批意见" sheetId="3" r:id="rId1"/>
-    <sheet name="成本一览表" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$K$55</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">成本一览表!$A$1:$K$7,成本一览表!$G$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">报销单与审批意见!$A$1:$L$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve"> {company}费用报销单</t>
   </si>
@@ -103,6 +101,9 @@
     <t>财务核定金额</t>
   </si>
   <si>
+    <t>费用承担部门</t>
+  </si>
+  <si>
     <t>{item.expItem}</t>
   </si>
   <si>
@@ -115,6 +116,9 @@
     <t>{item.verifyAmount}</t>
   </si>
   <si>
+    <t>{item.deptName}</t>
+  </si>
+  <si>
     <t>申请金额合计</t>
   </si>
   <si>
@@ -127,6 +131,9 @@
     <t>核定付款金额</t>
   </si>
   <si>
+    <t>进项税额合计</t>
+  </si>
+  <si>
     <t>核定冲账金额</t>
   </si>
   <si>
@@ -145,6 +152,9 @@
     <t>{verifyPayAmount}</t>
   </si>
   <si>
+    <t>{taxAmountTotal}</t>
+  </si>
+  <si>
     <t>审批意见</t>
   </si>
   <si>
@@ -164,64 +174,6 @@
   </si>
   <si>
     <t>{commentList.operateText}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">成本一览表
-</t>
-  </si>
-  <si>
-    <t>合同名称</t>
-  </si>
-  <si>
-    <t>费用类型</t>
-  </si>
-  <si>
-    <t>进项税</t>
-  </si>
-  <si>
-    <t>费用承担部门</t>
-  </si>
-  <si>
-    <t>{cost.htName}</t>
-  </si>
-  <si>
-    <t>{cost.htSn}</t>
-  </si>
-  <si>
-    <t>{cost.expItem}</t>
-  </si>
-  <si>
-    <t>{cost.descMemo}</t>
-  </si>
-  <si>
-    <t>{cost.applyAmount}</t>
-  </si>
-  <si>
-    <t>{cost.verifyAmount}</t>
-  </si>
-  <si>
-    <t>{cost.taxAmount}</t>
-  </si>
-  <si>
-    <t>{cost.deptName}</t>
-  </si>
-  <si>
-    <t>进项税额合计</t>
-  </si>
-  <si>
-    <t>{costApplyAmountTotal}</t>
-  </si>
-  <si>
-    <t>{costVerifyAmountTotal}</t>
-  </si>
-  <si>
-    <t>{costTaxAmountTotal}</t>
-  </si>
-  <si>
-    <t>公司名称</t>
-  </si>
-  <si>
-    <t>{company}</t>
   </si>
 </sst>
 </file>
@@ -237,7 +189,7 @@
     <numFmt numFmtId="177" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,27 +200,6 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="36"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="25"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -282,6 +213,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="25"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="26"/>
       <color theme="1"/>
@@ -290,6 +228,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="25"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -634,7 +578,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -646,43 +590,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -751,6 +658,21 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -767,6 +689,39 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -887,137 +842,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1027,11 +982,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1045,109 +997,115 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1518,49 +1476,55 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>985520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>67369</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1039091</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>33655</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>985520</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
+    <xdr:cxnSp>
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="直接连接符 9"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="0"/>
-          <a:ext cx="3524885" cy="1038860"/>
+          <a:off x="21078825" y="9112885"/>
+          <a:ext cx="3357880" cy="0"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom prst="line">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:prstClr val="black"/>
+          </a:solidFill>
+          <a:prstDash val="dash"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </xdr:spPr>
-    </xdr:pic>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1818,7 +1782,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="20.125" style="2" customWidth="1"/>
@@ -1832,293 +1796,315 @@
     <col min="9" max="9" width="22.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="20.375" style="2" customWidth="1"/>
     <col min="11" max="11" width="28.375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="12" max="12" width="45.625" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A1" s="16" t="s">
+    <row r="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:11">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+    <row r="2" ht="60" customHeight="1" spans="1:12">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:11">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
+    <row r="3" ht="60" customHeight="1" spans="1:12">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:11">
-      <c r="A4" s="5" t="s">
+    <row r="4" ht="60" customHeight="1" spans="1:12">
+      <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="7"/>
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="40" t="s">
+      <c r="K4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="40"/>
+      <c r="L4" s="38"/>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:11">
-      <c r="A5" s="17" t="s">
+    <row r="5" ht="60" customHeight="1" spans="1:12">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="19" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="19" t="s">
+      <c r="G5" s="12"/>
+      <c r="H5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="19" t="s">
+      <c r="I5" s="12"/>
+      <c r="J5" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="21"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:11">
-      <c r="A6" s="22" t="s">
+    <row r="6" ht="60" customHeight="1" spans="1:12">
+      <c r="A6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="23"/>
-      <c r="C6" s="22" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="24"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="25" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="17"/>
+      <c r="H6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="25" t="s">
+      <c r="I6" s="17"/>
+      <c r="J6" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="26"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="41"/>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:11">
-      <c r="A7" s="10" t="s">
+    <row r="7" ht="60" customHeight="1" spans="1:12">
+      <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="10" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="27" t="s">
+      <c r="I7" s="18"/>
+      <c r="J7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="41"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="42" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="8" ht="99.95" customHeight="1" spans="1:11">
-      <c r="A8" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="28" t="s">
+    <row r="8" ht="99.95" customHeight="1" spans="1:12">
+      <c r="A8" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="14" t="s">
+      <c r="B8" s="21"/>
+      <c r="C8" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="42" t="s">
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="43"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="23" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="10" t="s">
+    <row r="9" s="1" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="K9" s="10"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="23" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="60" customHeight="1" spans="1:11">
-      <c r="A10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="10" t="s">
+    <row r="10" s="1" customFormat="1" ht="60" customHeight="1" spans="1:12">
+      <c r="A10" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="14" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14" t="s">
+      <c r="D10" s="23"/>
+      <c r="E10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="14"/>
+      <c r="F10" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="11" ht="150" customHeight="1" spans="1:11">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
+    <row r="11" ht="150" customHeight="1" spans="1:12">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
     </row>
-    <row r="12" ht="90" customHeight="1" spans="1:11">
-      <c r="A12" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
+    <row r="12" ht="90" customHeight="1" spans="1:12">
+      <c r="A12" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:11">
-      <c r="A13" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
+    <row r="13" ht="60" customHeight="1" spans="1:12">
+      <c r="A13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:11">
-      <c r="A14" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="39"/>
+    <row r="14" ht="60" customHeight="1" spans="1:12">
+      <c r="A14" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="37"/>
+      <c r="G14" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="37">
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="K4:L4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J5:L5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J6:L6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="H7:I7"/>
@@ -2136,223 +2122,18 @@
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="H10:I10"/>
     <mergeCell ref="J10:K10"/>
-    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A12:L12"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="G13:L13"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="A1:K3"/>
+    <mergeCell ref="G14:L14"/>
+    <mergeCell ref="A1:L3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.984251968503937" bottom="0.984251968503937" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelRow="6"/>
-  <cols>
-    <col min="1" max="1" width="45.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="22.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="25.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="34.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24" style="2" customWidth="1"/>
-    <col min="11" max="11" width="32.625" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="132" customHeight="1" spans="1:11">
-      <c r="A1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" ht="99.95" customHeight="1" spans="1:11">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="15"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A3" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" ht="175" customHeight="1" spans="1:11">
-      <c r="A4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" ht="80.1" customHeight="1" spans="1:11">
-      <c r="A6" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-    </row>
-    <row r="7" ht="85" customHeight="1" spans="1:11">
-      <c r="A7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-    </row>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:K7"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0" right="0" top="0.748031496062992" bottom="0.748031496062992" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="32" orientation="portrait"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
